--- a/downloads/indicadores/BALANZA/BALANZA_datos.xlsx
+++ b/downloads/indicadores/BALANZA/BALANZA_datos.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -576,14 +576,14 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>May 24</t>
+          <t>Ene 18</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45413</v>
+        <v>43101</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>890.9759999999951</v>
+        <v>-4421.951000000005</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -634,18 +634,18 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Jun 24</t>
+          <t>Feb 18</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>45444</v>
+        <v>43132</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>-2406.323000000004</v>
+        <v>943.9329999999973</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-3,297 mdd</t>
+          <t>+5,366 mdd</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -692,18 +692,18 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Jul 24</t>
+          <t>Mar 18</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>45474</v>
+        <v>43160</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-1220.510999999999</v>
+        <v>1749.651000000005</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+1,186 mdd</t>
+          <t>+806 mdd</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -750,18 +750,18 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Ago 24</t>
+          <t>Abr 18</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>45505</v>
+        <v>43191</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>-5844.668000000005</v>
+        <v>-290.2709999999934</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>-4,624 mdd</t>
+          <t>-2,040 mdd</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -808,18 +808,18 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Sep 24</t>
+          <t>May 18</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>45536</v>
+        <v>43221</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>-1491.045999999995</v>
+        <v>-1552.329000000005</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>+4,354 mdd</t>
+          <t>-1,262 mdd</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -866,18 +866,18 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Oct 24</t>
+          <t>Jun 18</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>45566</v>
+        <v>43252</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>-211.3240000000005</v>
+        <v>-899.8289999999979</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>+1,280 mdd</t>
+          <t>+653 mdd</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -924,18 +924,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nov 24</t>
+          <t>Jul 18</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>45597</v>
+        <v>43282</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>-706.237000000001</v>
+        <v>-2869.906000000003</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>-495 mdd</t>
+          <t>-1,970 mdd</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -982,18 +982,18 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Dic 24</t>
+          <t>Ago 18</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>45627</v>
+        <v>43313</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1848.520999999993</v>
+        <v>-2584.288</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>+2,555 mdd</t>
+          <t>+286 mdd</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1040,18 +1040,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Ene 25</t>
+          <t>Sep 18</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>45658</v>
+        <v>43344</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-5213.209000000003</v>
+        <v>-301.0809999999983</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>-7,062 mdd</t>
+          <t>+2,283 mdd</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1098,18 +1098,18 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Feb 25</t>
+          <t>Oct 18</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>45689</v>
+        <v>43374</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>1654.228000000003</v>
+        <v>-2934.821000000004</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>+6,867 mdd</t>
+          <t>-2,634 mdd</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1156,18 +1156,18 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Mar 25</t>
+          <t>Nov 18</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>45717</v>
+        <v>43405</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>3289.771000000001</v>
+        <v>-2333.326999999997</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>+1,636 mdd</t>
+          <t>+601 mdd</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1214,18 +1214,18 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Abr 25</t>
+          <t>Dic 18</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>45748</v>
+        <v>43435</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>-44.46199999999953</v>
+        <v>1904.580000000002</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>-3,334 mdd</t>
+          <t>+4,238 mdd</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1272,18 +1272,18 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>May 25</t>
+          <t>Ene 19</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>45778</v>
+        <v>43466</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1231.824000000001</v>
+        <v>-4625.567999999999</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>+1,276 mdd</t>
+          <t>-6,530 mdd</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1330,18 +1330,18 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Jun 25</t>
+          <t>Feb 19</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>45809</v>
+        <v>43497</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>514.4289999999964</v>
+        <v>1363.910000000003</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>-717 mdd</t>
+          <t>+5,989 mdd</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1388,18 +1388,18 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Jul 25</t>
+          <t>Mar 19</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>45839</v>
+        <v>43525</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-16.69400000000314</v>
+        <v>1487.942000000003</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>-531 mdd</t>
+          <t>+124 mdd</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1446,18 +1446,18 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Ago 25</t>
+          <t>Abr 19</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>45870</v>
+        <v>43556</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>-1943.883999999998</v>
+        <v>1510.069000000003</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>-1,927 mdd</t>
+          <t>+22 mdd</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1504,18 +1504,18 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Sep 25</t>
+          <t>May 19</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>45901</v>
+        <v>43586</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>-2399.536999999997</v>
+        <v>957.1359999999986</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>-456 mdd</t>
+          <t>-553 mdd</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1562,18 +1562,18 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Jun 19</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>45931</v>
+        <v>43617</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>606.0680000000066</v>
+        <v>2542.241999999998</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>+3,006 mdd</t>
+          <t>+1,585 mdd</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1620,18 +1620,18 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Nov 25</t>
+          <t>Jul 19</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>45962</v>
+        <v>43647</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>662.7920000000013</v>
+        <v>-1290.542000000001</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>+57 mdd</t>
+          <t>-3,833 mdd</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1678,18 +1678,18 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Dic 25</t>
+          <t>Ago 19</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>45992</v>
+        <v>43678</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>2429.619999999995</v>
+        <v>402.708000000006</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>+1,767 mdd</t>
+          <t>+1,693 mdd</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1736,18 +1736,18 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Ene 26</t>
+          <t>Sep 19</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>46023</v>
+        <v>43709</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-6481.054000000004</v>
+        <v>-151.6010000000024</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>-8,911 mdd</t>
+          <t>-554 mdd</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1794,18 +1794,18 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Oct 19</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>46054</v>
+        <v>43739</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>-462.7779999999984</v>
+        <v>-687.4089999999997</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>+6,018 mdd</t>
+          <t>-536 mdd</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1852,18 +1852,18 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Nov 19</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>46082</v>
+        <v>43770</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>5931.998</v>
+        <v>786.8309999999983</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>+6,395 mdd</t>
+          <t>+1,474 mdd</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1910,18 +1910,18 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>Dic 19</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>46113</v>
+        <v>43800</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>4520.031000000003</v>
+        <v>3066.572</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>-1,412 mdd</t>
+          <t>+2,280 mdd</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1968,18 +1968,18 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>May 26 O</t>
+          <t>Ene 20</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>46143</v>
+        <v>43831</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>2259.167999999991</v>
+        <v>-2481.156999999999</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>-2,261 mdd</t>
+          <t>-5,548 mdd</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2026,56 +2026,4464 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
+          <t>Feb 20</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>43862</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2718.337999999996</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>+5,199 mdd</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mar 20</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>43891</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>3314.337</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>+596 mdd</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Abr 20</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>43922</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>-3234.394</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>-6,549 mdd</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>43952</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>-3462.294999999998</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>-228 mdd</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Jun 20</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>43983</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>5535.556999999997</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>+8,998 mdd</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Jul 20</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>44013</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>5655.041999999998</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>+119 mdd</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Ago 20</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>44044</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>6155.397999999997</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>+500 mdd</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sep 20</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>44075</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>4397.137999999999</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>-1,758 mdd</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Oct 20</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>44105</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>6256.005000000005</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>+1,859 mdd</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nov 20</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>44136</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>3056.154999999999</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>-3,200 mdd</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Dic 20</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>44166</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>6274.687000000005</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>+3,219 mdd</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Ene 21</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>-1194.610999999997</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>-7,469 mdd</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Feb 21</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>44228</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>2727.008000000002</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>+3,922 mdd</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Mar 21</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>44256</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>-2944.473999999995</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>-5,671 mdd</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Abr 21</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>44287</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>1684.881000000001</v>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>+4,629 mdd</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>44317</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>386.9159999999974</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>-1,298 mdd</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>44348</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>709.9440000000031</v>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>+323 mdd</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Jul 21</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>-3997.671999999999</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>-4,708 mdd</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Ago 21</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>44409</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>-3744.258999999998</v>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>+253 mdd</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Sep 21</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>44440</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>-2324.093000000001</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>+1,420 mdd</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Oct 21</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>-2799.347999999998</v>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>-475 mdd</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Nov 21</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>44501</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>-22.1160000000018</v>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>+2,777 mdd</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Dic 21</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>44531</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>763.7419999999984</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>+786 mdd</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Ene 22</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>-6262.324000000001</v>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>-7,026 mdd</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Feb 22</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>44593</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>1335.404000000002</v>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>+7,598 mdd</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>44621</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>147.1589999999997</v>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>-1,188 mdd</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Abr 22</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>44652</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>-1783.032999999996</v>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>-1,930 mdd</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>44682</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>-2255.710999999996</v>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>-473 mdd</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>44713</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>-3971.163</v>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>-1,715 mdd</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Jul 22</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>-6247.436000000002</v>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>-2,276 mdd</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Ago 22</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>44774</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>-5703.967000000004</v>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>+543 mdd</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Sep 22</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>44805</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>-1196.663999999997</v>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>+4,507 mdd</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Oct 22</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>44835</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>-2662.834000000003</v>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>-1,466 mdd</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Nov 22</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>44866</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>-450.1720000000059</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>+2,213 mdd</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Dic 22</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>44896</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>942.8549999999959</v>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>+1,393 mdd</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Ene 23</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>-4129.334000000003</v>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>-5,072 mdd</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Feb 23</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>44958</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>-1985.841999999997</v>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>+2,143 mdd</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>44986</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>1160.462</v>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>+3,146 mdd</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Abr 23</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>45017</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>-1646.189000000006</v>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>-2,807 mdd</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>45047</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>-194.3240000000005</v>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>+1,452 mdd</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>45078</v>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>-186.4959999999992</v>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>+8 mdd</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Jul 23</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>-840.7829999999958</v>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>-654 mdd</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Ago 23</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>45139</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>-2116.864000000001</v>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>-1,276 mdd</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Sep 23</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>45170</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>-2661.324000000001</v>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>-544 mdd</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Oct 23</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>45200</v>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>-1806.218999999997</v>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>+855 mdd</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Nov 23</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>45231</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>-770.5380000000005</v>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>+1,036 mdd</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Dic 23</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>2898.948000000004</v>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>+3,669 mdd</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Ene 24</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>-5084.036</v>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>-7,983 mdd</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Feb 24</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>45323</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>-1429.919999999998</v>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>+3,654 mdd</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Mar 24</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>1534.340000000004</v>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>+2,964 mdd</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Abr 24</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>45383</v>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>-4420.712</v>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>-5,955 mdd</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>May 24</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>45413</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>890.9759999999951</v>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>+5,312 mdd</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>45444</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>-2406.323000000004</v>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>-3,297 mdd</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Jul 24</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>-1220.510999999999</v>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>+1,186 mdd</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Ago 24</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>45505</v>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>-5844.668000000005</v>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>-4,624 mdd</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Sep 24</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>45536</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>-1491.045999999995</v>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>+4,354 mdd</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Oct 24</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>-211.3240000000005</v>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>+1,280 mdd</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Nov 24</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>45597</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>-706.237000000001</v>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>-495 mdd</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Dic 24</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>45627</v>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>1848.520999999993</v>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>+2,555 mdd</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Ene 25</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>-5213.209000000003</v>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>-7,062 mdd</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Feb 25</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>45689</v>
+      </c>
+      <c r="C91" s="9" t="n">
+        <v>1654.228000000003</v>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>+6,867 mdd</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>45717</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>3289.771000000001</v>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>+1,636 mdd</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Abr 25</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>-44.46199999999953</v>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>-3,334 mdd</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>May 25</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>1231.824000000001</v>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>+1,276 mdd</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>514.4289999999964</v>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>-717 mdd</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Jul 25</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>-16.69400000000314</v>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>-531 mdd</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Ago 25</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>-1943.883999999998</v>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>-1,927 mdd</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>-2399.536999999997</v>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>-456 mdd</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>606.0680000000066</v>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>+3,006 mdd</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Nov 25</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>662.7920000000013</v>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>+57 mdd</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Dic 25</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C101" s="9" t="n">
+        <v>2429.619999999995</v>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>+1,767 mdd</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Ene 26</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>-6481.054000000004</v>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>-8,911 mdd</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>-462.7779999999984</v>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>+6,018 mdd</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>5931.998</v>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>+6,395 mdd</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>4520.031000000003</v>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>-1,412 mdd</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>May 26 O</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>2259.167999999991</v>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>-2,261 mdd</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
+      <c r="B107" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C107" s="9" t="n">
         <v>4089.895999999993</v>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t>+1,831 mdd</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>Millones de dólares</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>Serie original</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+        </is>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
         <is>
           <t>27 de julio de 2026</t>
         </is>
